--- a/20_設計書/課題リスト.xlsx
+++ b/20_設計書/課題リスト.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AMA1040\Documents\古竹作成\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A1E5399-DA05-4585-BFBD-DED5999CA526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDBDA689-3279-4C2D-AA1C-39266BE61F28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="859" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30510" yWindow="1710" windowWidth="20595" windowHeight="13245" tabRatio="859" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="課題リスト" sheetId="78" r:id="rId1"/>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="64">
   <si>
     <t>項番</t>
     <rPh sb="0" eb="2">
@@ -205,13 +205,6 @@
     <phoneticPr fontId="40"/>
   </si>
   <si>
-    <t>CSVボタンを追加しました。</t>
-    <rPh sb="7" eb="9">
-      <t>ツイカ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
     <t>期間指定してCSVダウンロードができれば画面確認は不要です。</t>
     <rPh sb="0" eb="4">
       <t>キカンシテイ</t>
@@ -266,28 +259,6 @@
     </rPh>
     <rPh sb="12" eb="16">
       <t>ニチエイヘイキ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>化学物質データ画面から遷移dするのではなく、別でURLの管理をしたい。</t>
-    <rPh sb="0" eb="2">
-      <t>カガク</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ブッシツ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>センイ</t>
-    </rPh>
-    <rPh sb="22" eb="23">
-      <t>ベツ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>カンリ</t>
     </rPh>
     <phoneticPr fontId="40"/>
   </si>
@@ -401,13 +372,6 @@
     <phoneticPr fontId="40"/>
   </si>
   <si>
-    <t>エラーメッセージエリアを削除いたしました。</t>
-    <rPh sb="12" eb="14">
-      <t>サクジョ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
     <t>提出企業名とエンドユーザーの表組を広げてほしい。</t>
     <rPh sb="0" eb="5">
       <t>テイシュツキギョウメイ</t>
@@ -485,44 +449,6 @@
     <phoneticPr fontId="40"/>
   </si>
   <si>
-    <t>現時点ではDBに申請ログのデータを保存して、削除予定はありません。</t>
-    <rPh sb="0" eb="3">
-      <t>ゲンジテン</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>シンセイ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>ホゾン</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>ヨテイ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>「2.環境証明書申請状況詳細」が不要という認識でよろしいでしょうか。</t>
-    <rPh sb="3" eb="8">
-      <t>カンキョウショウメイショ</t>
-    </rPh>
-    <rPh sb="8" eb="12">
-      <t>シンセイジョウキョウ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ショウサイ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>フヨウ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>ニンシキ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
     <t>CLコード名の重複は処理対象外で不要です。</t>
     <rPh sb="5" eb="6">
       <t>メイ</t>
@@ -647,35 +573,6 @@
     <phoneticPr fontId="40"/>
   </si>
   <si>
-    <t>画面全体で1つのスクロールにすっように変更しました。</t>
-    <rPh sb="0" eb="4">
-      <t>ガメンゼンタイ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>ヘンコウ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
-    <t>色変更のほかに太字、リンク挿入機能を追加しました。</t>
-    <rPh sb="0" eb="3">
-      <t>イロヘンコウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>フトジ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ソウニュウ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>キノウ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>ツイカ</t>
-    </rPh>
-    <phoneticPr fontId="40"/>
-  </si>
-  <si>
     <t>バッチを利用しない方法で更新できる方法を取ります。</t>
     <rPh sb="4" eb="6">
       <t>リヨウ</t>
@@ -792,6 +689,387 @@
     </rPh>
     <rPh sb="16" eb="18">
       <t>ヘイキ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>ログイン機能</t>
+    <rPh sb="4" eb="6">
+      <t>キノウ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>別システムにて行う予定だが、仕様不明のため現状進展がない認識です。</t>
+    <rPh sb="0" eb="1">
+      <t>ベツ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヨテイ</t>
+    </rPh>
+    <rPh sb="14" eb="18">
+      <t>シヨウフメイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ゲンジョウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>シンテン</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ニンシキ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>検討中</t>
+    <rPh sb="0" eb="3">
+      <t>ケントウチュウ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>色変更のほかに太字を想定、リンク挿入機能は検討中。</t>
+    <rPh sb="0" eb="3">
+      <t>イロヘンコウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>フトジ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ソウテイ</t>
+    </rPh>
+    <rPh sb="16" eb="20">
+      <t>ソウニュウキノウ</t>
+    </rPh>
+    <rPh sb="21" eb="24">
+      <t>ケントウチュウ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>二次フェーズでの対応でお願いいたします。</t>
+    <rPh sb="0" eb="2">
+      <t>ニジ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>タイオウ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ネガ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>化学物質データ画面から遷移するのではなく、別でURLの管理をしたい。</t>
+    <rPh sb="0" eb="2">
+      <t>カガク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ブッシツ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ベツ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>エラーメッセージエリアを削除いたしました。エラーメッセージ自体はポップアップ表示で行います。</t>
+    <rPh sb="12" eb="14">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ジタイ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>画面全体で1つのスクロールにするように変更しました。</t>
+    <rPh sb="0" eb="4">
+      <t>ガメンゼンタイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>項番1より不要のため該当箇所をグレーアウトしました。</t>
+    <rPh sb="0" eb="2">
+      <t>コウバン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>フヨウ</t>
+    </rPh>
+    <rPh sb="10" eb="14">
+      <t>ガイトウカショ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>不要のため該当箇所をグレーアウトしました。</t>
+    <rPh sb="0" eb="2">
+      <t>フヨウ</t>
+    </rPh>
+    <rPh sb="5" eb="9">
+      <t>ガイトウカショ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>不要の文言箇所に取り消し線を引きました。</t>
+    <rPh sb="0" eb="2">
+      <t>フヨウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>モンゴン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カショ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ケ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>セン</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ヒ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>バッチ処理/環境証明書申請完了</t>
+    <rPh sb="3" eb="5">
+      <t>ショリ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>環境証明書申請完了時および環境証明書取込バッチ実行時のメール詳細を確認したいため以下の資料をご連携お願いいたします。
+①「SEML020 環境証明書取込完了メール」
+②「SEML030　環境証明書申請完了お知らせメール」</t>
+    <rPh sb="0" eb="7">
+      <t>カンキョウショウメイショシンセイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カンキョウ</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>ショウメイショ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>トリコミ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>シリョウ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>レンケイ</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>ネガ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>現時点ではDBに申請ログのデータを保存して、保存データの削除予定はありません。</t>
+    <rPh sb="0" eb="3">
+      <t>ゲンジテン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>シンセイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ホゾン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ホゾン</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ヨテイ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>指摘レビューにおいてHRSロゴ画像のファイルが文字列となり取込できなかったため、別途画像ファイルをご連携お願いいたします。</t>
+    <rPh sb="0" eb="2">
+      <t>シテキ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="23" eb="26">
+      <t>モジレツ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>トリコミ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ベット</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>レンケイ</t>
+    </rPh>
+    <rPh sb="53" eb="54">
+      <t>ネガ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>ER図</t>
+    <rPh sb="2" eb="3">
+      <t>ズ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>項番1の仕様次第で変更されるので機能詳細が確定するまで保留です。</t>
+    <rPh sb="0" eb="2">
+      <t>コウバン</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>シヨウシダイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="16" eb="20">
+      <t>キノウショウサイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>カクテイ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ホリュウ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <t>CSVダウンロードボタンを追加しました。</t>
+    <rPh sb="13" eb="15">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="40"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ヒロセ電機　浅尾様</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">
+画面確認ですが「2.環境証明書申請状況詳細」が不要という認識でよろしいでしょうか。
+上記認識に相違ない場合、画面確認不要にする必要はないと感じております。</t>
+    </r>
+    <rPh sb="3" eb="5">
+      <t>デンキ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>アサオサマ</t>
+    </rPh>
+    <rPh sb="10" eb="14">
+      <t>ガメンカクニン</t>
+    </rPh>
+    <rPh sb="20" eb="25">
+      <t>カンキョウショウメイショ</t>
+    </rPh>
+    <rPh sb="25" eb="29">
+      <t>シンセイジョウキョウ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>フヨウ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ニンシキ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>ジョウキ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>ニンシキ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>ソウイ</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="64" eb="68">
+      <t>ガメンカクニン</t>
+    </rPh>
+    <rPh sb="68" eb="70">
+      <t>フヨウ</t>
+    </rPh>
+    <rPh sb="73" eb="75">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="79" eb="80">
+      <t>カン</t>
     </rPh>
     <phoneticPr fontId="40"/>
   </si>
@@ -805,7 +1083,7 @@
     <numFmt numFmtId="177" formatCode="0.00_)"/>
     <numFmt numFmtId="178" formatCode="#,##0.00;[Red]\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="45">
+  <fonts count="46">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1124,8 +1402,15 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1192,12 +1477,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -1775,7 +2054,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1805,12 +2084,6 @@
     </xf>
     <xf numFmtId="0" fontId="43" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="186">
@@ -2348,7 +2621,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7D65F84-4143-485E-A686-A2B54498E502}">
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="4.90625" style="6" bestFit="1" customWidth="1"/>
@@ -2358,7 +2631,7 @@
     <col min="5" max="5" width="53.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.5" customHeight="1">
+    <row r="1" spans="1:7" ht="21.5" customHeight="1">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -2381,21 +2654,21 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="21.5" customHeight="1">
+    <row r="2" spans="1:7">
       <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="C2" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>46</v>
+      <c r="E2" s="8" t="s">
+        <v>39</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>5</v>
@@ -2404,162 +2677,153 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="21.5" customHeight="1">
+    <row r="3" spans="1:7">
       <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="B3" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="9"/>
+      <c r="F3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="G3" s="2" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="35" customHeight="1">
+    <row r="4" spans="1:7" ht="50">
       <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>16</v>
+      <c r="B4" s="8" t="s">
+        <v>56</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="8"/>
+      <c r="F4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="G4" s="1" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="21.5" customHeight="1">
+    <row r="5" spans="1:7">
       <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="B5" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="9"/>
       <c r="F5" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="10"/>
+        <v>47</v>
+      </c>
     </row>
-    <row r="6" spans="1:8" ht="21.5" customHeight="1">
+    <row r="6" spans="1:7">
       <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="B6" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>17</v>
+      <c r="E6" s="8" t="s">
+        <v>48</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="21.5" customHeight="1">
+    <row r="7" spans="1:7" ht="25">
       <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="C7" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>36</v>
+      <c r="E7" s="9" t="s">
+        <v>52</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" s="10"/>
+        <v>14</v>
+      </c>
     </row>
-    <row r="8" spans="1:8" ht="33" customHeight="1">
+    <row r="8" spans="1:7" ht="25">
       <c r="A8" s="4">
         <v>7</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="1" t="s">
+      <c r="B8" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>12</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H8" s="11"/>
+        <v>14</v>
+      </c>
     </row>
-    <row r="9" spans="1:8" ht="34" customHeight="1">
+    <row r="9" spans="1:7">
       <c r="A9" s="5">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" s="2" t="s">
+      <c r="B9" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>12</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>13</v>
@@ -2568,44 +2832,44 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="38.5" customHeight="1">
+    <row r="10" spans="1:7" ht="50">
       <c r="A10" s="4">
         <v>9</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>19</v>
+      <c r="E10" s="8" t="s">
+        <v>63</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="38" customHeight="1">
+    <row r="11" spans="1:7" ht="25">
       <c r="A11" s="5">
         <v>10</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>30</v>
+      <c r="E11" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>13</v>
@@ -2614,21 +2878,21 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="21.5" customHeight="1">
+    <row r="12" spans="1:7">
       <c r="A12" s="4">
         <v>11</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" s="1" t="s">
+      <c r="B12" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>32</v>
+      <c r="E12" s="8" t="s">
+        <v>37</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>13</v>
@@ -2637,118 +2901,134 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="28.5" customHeight="1">
+    <row r="13" spans="1:7" ht="25">
       <c r="A13" s="5">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>28</v>
+      <c r="B13" s="9" t="s">
+        <v>19</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E13" s="2"/>
+        <v>25</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>18</v>
+      </c>
       <c r="F13" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="10"/>
+        <v>13</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="14" spans="1:8" ht="28.5" customHeight="1">
+    <row r="14" spans="1:7" ht="25">
       <c r="A14" s="4">
         <v>13</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>28</v>
+      <c r="B14" s="8" t="s">
+        <v>19</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="8"/>
+      <c r="F14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="10"/>
+      <c r="G14" s="1" t="s">
+        <v>47</v>
+      </c>
     </row>
-    <row r="15" spans="1:8" ht="21.5" customHeight="1">
+    <row r="15" spans="1:7" ht="25">
       <c r="A15" s="5">
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" s="2" t="s">
+      <c r="B15" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="10"/>
+      <c r="E15" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="16" spans="1:8" ht="21.5" customHeight="1">
+    <row r="16" spans="1:7">
       <c r="A16" s="4">
         <v>15</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="10"/>
+      <c r="E16" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="17" spans="1:7" ht="21.5" customHeight="1">
+    <row r="17" spans="1:7" ht="25">
       <c r="A17" s="5">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>47</v>
+      <c r="B17" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>49</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="21.5" customHeight="1">
+    <row r="18" spans="1:7">
       <c r="A18" s="4">
         <v>17</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D18" s="1" t="s">
+      <c r="B18" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>49</v>
+      <c r="E18" s="8" t="s">
+        <v>55</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>13</v>
@@ -2757,55 +3037,147 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="21.5" customHeight="1">
+    <row r="19" spans="1:7">
       <c r="A19" s="5">
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>40</v>
+      <c r="B19" s="9" t="s">
+        <v>26</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D19" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>51</v>
+      <c r="E19" s="9" t="s">
+        <v>54</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="21.5" customHeight="1">
-      <c r="A20" s="4"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
+    <row r="20" spans="1:7">
+      <c r="A20" s="4">
+        <v>19</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="21" spans="1:7" ht="21.5" customHeight="1">
-      <c r="A21" s="5"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
+    <row r="21" spans="1:7">
+      <c r="A21" s="5">
+        <v>20</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="22" spans="1:7" ht="21.5" customHeight="1">
-      <c r="A22" s="4"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
+      <c r="A22" s="4">
+        <v>21</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="21.5" customHeight="1">
+      <c r="A23" s="5">
+        <v>22</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="21.5" customHeight="1">
+      <c r="A24" s="4"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+    </row>
+    <row r="25" spans="1:7" ht="21.5" customHeight="1">
+      <c r="A25" s="5"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+    </row>
+    <row r="26" spans="1:7" ht="21.5" customHeight="1">
+      <c r="A26" s="4"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="40"/>
